--- a/Documentation/User Manual Source/pto-behavior.xlsx
+++ b/Documentation/User Manual Source/pto-behavior.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michaelkrisper\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QUAM\Workspace\VECTO_quam\Documentation\User Manual Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -170,7 +170,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -405,10 +405,10 @@
                   <c:v>990</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>911.32429999999999</c:v>
+                  <c:v>716</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>716.32429999999999</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>600</c:v>
@@ -833,7 +833,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -871,7 +871,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="471600208"/>
@@ -958,7 +958,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -996,7 +996,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="471600536"/>
@@ -1037,7 +1037,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2627,7 +2627,7 @@
         <v>16</v>
       </c>
       <c r="F16">
-        <v>911.32429999999999</v>
+        <v>716</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2635,7 +2635,7 @@
         <v>18</v>
       </c>
       <c r="F17">
-        <v>716.32429999999999</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
